--- a/output/upload/S00027_2259_바로연금보험_무배당.xlsx
+++ b/output/upload/S00027_2259_바로연금보험_무배당.xlsx
@@ -2611,17 +2611,9 @@
     </row>
     <row r="7">
       <c r="A7" s="5" t="n"/>
-      <c r="B7" s="5" t="inlineStr">
-        <is>
-          <t>2259804</t>
-        </is>
-      </c>
+      <c r="B7" s="5" t="inlineStr"/>
       <c r="C7" s="5" t="n"/>
-      <c r="D7" s="5" t="inlineStr">
-        <is>
-          <t>2259804</t>
-        </is>
-      </c>
+      <c r="D7" s="5" t="inlineStr"/>
       <c r="E7" s="5" t="n"/>
       <c r="F7" s="5" t="n"/>
       <c r="G7" s="6" t="inlineStr">

--- a/output/upload/S00027_2259_바로연금보험_무배당.xlsx
+++ b/output/upload/S00027_2259_바로연금보험_무배당.xlsx
@@ -2611,11 +2611,31 @@
     </row>
     <row r="7">
       <c r="A7" s="5" t="n"/>
-      <c r="B7" s="5" t="inlineStr"/>
-      <c r="C7" s="5" t="n"/>
-      <c r="D7" s="5" t="inlineStr"/>
-      <c r="E7" s="5" t="n"/>
-      <c r="F7" s="5" t="n"/>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>2259801</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 바로연금보험 무배당(종신연금형 일반형 개인형)</t>
+        </is>
+      </c>
+      <c r="D7" s="5" t="inlineStr">
+        <is>
+          <t>2259801</t>
+        </is>
+      </c>
+      <c r="E7" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 바로연금보험 무배당(종신연금형 일반형 개인형)</t>
+        </is>
+      </c>
+      <c r="F7" s="5" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
       <c r="G7" s="6" t="inlineStr">
         <is>
           <t>20260101</t>

--- a/output/upload/S00027_2259_바로연금보험_무배당.xlsx
+++ b/output/upload/S00027_2259_바로연금보험_무배당.xlsx
@@ -499,7 +499,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW14"/>
+  <dimension ref="A1:AW63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17.484375" customWidth="1" min="1" max="1"/>
@@ -2714,20 +2714,72 @@
     </row>
     <row r="8">
       <c r="A8" s="5" t="n"/>
-      <c r="B8" s="5" t="n"/>
-      <c r="C8" s="5" t="n"/>
-      <c r="D8" s="5" t="n"/>
-      <c r="E8" s="5" t="n"/>
-      <c r="F8" s="5" t="n"/>
-      <c r="G8" s="6" t="n"/>
-      <c r="H8" s="6" t="n"/>
-      <c r="I8" s="6" t="n"/>
-      <c r="J8" s="6" t="n"/>
-      <c r="K8" s="6" t="n"/>
-      <c r="L8" s="6" t="n"/>
-      <c r="M8" s="6" t="n"/>
-      <c r="N8" s="6" t="n"/>
-      <c r="O8" s="6" t="n"/>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>2259801</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 바로연금보험 무배당(종신연금형 일반형 개인형)</t>
+        </is>
+      </c>
+      <c r="D8" s="5" t="inlineStr">
+        <is>
+          <t>2259801</t>
+        </is>
+      </c>
+      <c r="E8" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 바로연금보험 무배당(종신연금형 일반형 개인형)</t>
+        </is>
+      </c>
+      <c r="F8" s="5" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
+      <c r="G8" s="6" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H8" s="6" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I8" s="6" t="inlineStr">
+        <is>
+          <t>X50</t>
+        </is>
+      </c>
+      <c r="J8" s="6" t="inlineStr">
+        <is>
+          <t>N0</t>
+        </is>
+      </c>
+      <c r="K8" s="6" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L8" s="6" t="n">
+        <v>50</v>
+      </c>
+      <c r="M8" s="6" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N8" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O8" s="6" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
       <c r="P8" s="6" t="n"/>
       <c r="Q8" s="6" t="n"/>
       <c r="R8" s="6" t="n"/>
@@ -2765,20 +2817,72 @@
     </row>
     <row r="9">
       <c r="A9" s="5" t="n"/>
-      <c r="B9" s="5" t="n"/>
-      <c r="C9" s="5" t="n"/>
-      <c r="D9" s="5" t="n"/>
-      <c r="E9" s="5" t="n"/>
-      <c r="F9" s="5" t="n"/>
-      <c r="G9" s="6" t="n"/>
-      <c r="H9" s="6" t="n"/>
-      <c r="I9" s="6" t="n"/>
-      <c r="J9" s="6" t="n"/>
-      <c r="K9" s="6" t="n"/>
-      <c r="L9" s="6" t="n"/>
-      <c r="M9" s="6" t="n"/>
-      <c r="N9" s="6" t="n"/>
-      <c r="O9" s="6" t="n"/>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>2259801</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 바로연금보험 무배당(종신연금형 일반형 개인형)</t>
+        </is>
+      </c>
+      <c r="D9" s="5" t="inlineStr">
+        <is>
+          <t>2259801</t>
+        </is>
+      </c>
+      <c r="E9" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 바로연금보험 무배당(종신연금형 일반형 개인형)</t>
+        </is>
+      </c>
+      <c r="F9" s="5" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
+      <c r="G9" s="6" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H9" s="6" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I9" s="6" t="inlineStr">
+        <is>
+          <t>X51</t>
+        </is>
+      </c>
+      <c r="J9" s="6" t="inlineStr">
+        <is>
+          <t>N0</t>
+        </is>
+      </c>
+      <c r="K9" s="6" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L9" s="6" t="n">
+        <v>51</v>
+      </c>
+      <c r="M9" s="6" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N9" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O9" s="6" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
       <c r="P9" s="6" t="n"/>
       <c r="Q9" s="6" t="n"/>
       <c r="R9" s="6" t="n"/>
@@ -2816,20 +2920,72 @@
     </row>
     <row r="10">
       <c r="A10" s="5" t="n"/>
-      <c r="B10" s="5" t="n"/>
-      <c r="C10" s="5" t="n"/>
-      <c r="D10" s="5" t="n"/>
-      <c r="E10" s="5" t="n"/>
-      <c r="F10" s="5" t="n"/>
-      <c r="G10" s="6" t="n"/>
-      <c r="H10" s="6" t="n"/>
-      <c r="I10" s="6" t="n"/>
-      <c r="J10" s="6" t="n"/>
-      <c r="K10" s="6" t="n"/>
-      <c r="L10" s="6" t="n"/>
-      <c r="M10" s="6" t="n"/>
-      <c r="N10" s="6" t="n"/>
-      <c r="O10" s="6" t="n"/>
+      <c r="B10" s="5" t="inlineStr">
+        <is>
+          <t>2259801</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 바로연금보험 무배당(종신연금형 일반형 개인형)</t>
+        </is>
+      </c>
+      <c r="D10" s="5" t="inlineStr">
+        <is>
+          <t>2259801</t>
+        </is>
+      </c>
+      <c r="E10" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 바로연금보험 무배당(종신연금형 일반형 개인형)</t>
+        </is>
+      </c>
+      <c r="F10" s="5" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
+      <c r="G10" s="6" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H10" s="6" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I10" s="6" t="inlineStr">
+        <is>
+          <t>X52</t>
+        </is>
+      </c>
+      <c r="J10" s="6" t="inlineStr">
+        <is>
+          <t>N0</t>
+        </is>
+      </c>
+      <c r="K10" s="6" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L10" s="6" t="n">
+        <v>52</v>
+      </c>
+      <c r="M10" s="6" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N10" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O10" s="6" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
       <c r="P10" s="6" t="n"/>
       <c r="Q10" s="6" t="n"/>
       <c r="R10" s="6" t="n"/>
@@ -2867,20 +3023,72 @@
     </row>
     <row r="11">
       <c r="A11" s="5" t="n"/>
-      <c r="B11" s="5" t="n"/>
-      <c r="C11" s="5" t="n"/>
-      <c r="D11" s="5" t="n"/>
-      <c r="E11" s="5" t="n"/>
-      <c r="F11" s="5" t="n"/>
-      <c r="G11" s="6" t="n"/>
-      <c r="H11" s="6" t="n"/>
-      <c r="I11" s="6" t="n"/>
-      <c r="J11" s="6" t="n"/>
-      <c r="K11" s="6" t="n"/>
-      <c r="L11" s="6" t="n"/>
-      <c r="M11" s="6" t="n"/>
-      <c r="N11" s="6" t="n"/>
-      <c r="O11" s="6" t="n"/>
+      <c r="B11" s="5" t="inlineStr">
+        <is>
+          <t>2259801</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 바로연금보험 무배당(종신연금형 일반형 개인형)</t>
+        </is>
+      </c>
+      <c r="D11" s="5" t="inlineStr">
+        <is>
+          <t>2259801</t>
+        </is>
+      </c>
+      <c r="E11" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 바로연금보험 무배당(종신연금형 일반형 개인형)</t>
+        </is>
+      </c>
+      <c r="F11" s="5" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
+      <c r="G11" s="6" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H11" s="6" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I11" s="6" t="inlineStr">
+        <is>
+          <t>X53</t>
+        </is>
+      </c>
+      <c r="J11" s="6" t="inlineStr">
+        <is>
+          <t>N0</t>
+        </is>
+      </c>
+      <c r="K11" s="6" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L11" s="6" t="n">
+        <v>53</v>
+      </c>
+      <c r="M11" s="6" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N11" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O11" s="6" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
       <c r="P11" s="6" t="n"/>
       <c r="Q11" s="6" t="n"/>
       <c r="R11" s="6" t="n"/>
@@ -2918,20 +3126,72 @@
     </row>
     <row r="12">
       <c r="A12" s="5" t="n"/>
-      <c r="B12" s="5" t="n"/>
-      <c r="C12" s="5" t="n"/>
-      <c r="D12" s="5" t="n"/>
-      <c r="E12" s="5" t="n"/>
-      <c r="F12" s="5" t="n"/>
-      <c r="G12" s="6" t="n"/>
-      <c r="H12" s="6" t="n"/>
-      <c r="I12" s="6" t="n"/>
-      <c r="J12" s="6" t="n"/>
-      <c r="K12" s="6" t="n"/>
-      <c r="L12" s="6" t="n"/>
-      <c r="M12" s="6" t="n"/>
-      <c r="N12" s="6" t="n"/>
-      <c r="O12" s="6" t="n"/>
+      <c r="B12" s="5" t="inlineStr">
+        <is>
+          <t>2259801</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 바로연금보험 무배당(종신연금형 일반형 개인형)</t>
+        </is>
+      </c>
+      <c r="D12" s="5" t="inlineStr">
+        <is>
+          <t>2259801</t>
+        </is>
+      </c>
+      <c r="E12" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 바로연금보험 무배당(종신연금형 일반형 개인형)</t>
+        </is>
+      </c>
+      <c r="F12" s="5" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
+      <c r="G12" s="6" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H12" s="6" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I12" s="6" t="inlineStr">
+        <is>
+          <t>X54</t>
+        </is>
+      </c>
+      <c r="J12" s="6" t="inlineStr">
+        <is>
+          <t>N0</t>
+        </is>
+      </c>
+      <c r="K12" s="6" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L12" s="6" t="n">
+        <v>54</v>
+      </c>
+      <c r="M12" s="6" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N12" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O12" s="6" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
       <c r="P12" s="6" t="n"/>
       <c r="Q12" s="6" t="n"/>
       <c r="R12" s="6" t="n"/>
@@ -2969,20 +3229,72 @@
     </row>
     <row r="13">
       <c r="A13" s="5" t="n"/>
-      <c r="B13" s="5" t="n"/>
-      <c r="C13" s="5" t="n"/>
-      <c r="D13" s="5" t="n"/>
-      <c r="E13" s="5" t="n"/>
-      <c r="F13" s="5" t="n"/>
-      <c r="G13" s="6" t="n"/>
-      <c r="H13" s="6" t="n"/>
-      <c r="I13" s="6" t="n"/>
-      <c r="J13" s="6" t="n"/>
-      <c r="K13" s="6" t="n"/>
-      <c r="L13" s="6" t="n"/>
-      <c r="M13" s="6" t="n"/>
-      <c r="N13" s="6" t="n"/>
-      <c r="O13" s="6" t="n"/>
+      <c r="B13" s="5" t="inlineStr">
+        <is>
+          <t>2259801</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 바로연금보험 무배당(종신연금형 일반형 개인형)</t>
+        </is>
+      </c>
+      <c r="D13" s="5" t="inlineStr">
+        <is>
+          <t>2259801</t>
+        </is>
+      </c>
+      <c r="E13" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 바로연금보험 무배당(종신연금형 일반형 개인형)</t>
+        </is>
+      </c>
+      <c r="F13" s="5" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
+      <c r="G13" s="6" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H13" s="6" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I13" s="6" t="inlineStr">
+        <is>
+          <t>X55</t>
+        </is>
+      </c>
+      <c r="J13" s="6" t="inlineStr">
+        <is>
+          <t>N0</t>
+        </is>
+      </c>
+      <c r="K13" s="6" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L13" s="6" t="n">
+        <v>55</v>
+      </c>
+      <c r="M13" s="6" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N13" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O13" s="6" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
       <c r="P13" s="6" t="n"/>
       <c r="Q13" s="6" t="n"/>
       <c r="R13" s="6" t="n"/>
@@ -3020,20 +3332,72 @@
     </row>
     <row r="14">
       <c r="A14" s="5" t="n"/>
-      <c r="B14" s="5" t="n"/>
-      <c r="C14" s="5" t="n"/>
-      <c r="D14" s="5" t="n"/>
-      <c r="E14" s="5" t="n"/>
-      <c r="F14" s="5" t="n"/>
-      <c r="G14" s="6" t="n"/>
-      <c r="H14" s="6" t="n"/>
-      <c r="I14" s="6" t="n"/>
-      <c r="J14" s="6" t="n"/>
-      <c r="K14" s="6" t="n"/>
-      <c r="L14" s="6" t="n"/>
-      <c r="M14" s="6" t="n"/>
-      <c r="N14" s="6" t="n"/>
-      <c r="O14" s="6" t="n"/>
+      <c r="B14" s="5" t="inlineStr">
+        <is>
+          <t>2259801</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 바로연금보험 무배당(종신연금형 일반형 개인형)</t>
+        </is>
+      </c>
+      <c r="D14" s="5" t="inlineStr">
+        <is>
+          <t>2259801</t>
+        </is>
+      </c>
+      <c r="E14" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 바로연금보험 무배당(종신연금형 일반형 개인형)</t>
+        </is>
+      </c>
+      <c r="F14" s="5" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
+      <c r="G14" s="6" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H14" s="6" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I14" s="6" t="inlineStr">
+        <is>
+          <t>X56</t>
+        </is>
+      </c>
+      <c r="J14" s="6" t="inlineStr">
+        <is>
+          <t>N0</t>
+        </is>
+      </c>
+      <c r="K14" s="6" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L14" s="6" t="n">
+        <v>56</v>
+      </c>
+      <c r="M14" s="6" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N14" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O14" s="6" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
       <c r="P14" s="6" t="n"/>
       <c r="Q14" s="6" t="n"/>
       <c r="R14" s="6" t="n"/>
@@ -3069,6 +3433,3338 @@
       <c r="AV14" s="6" t="n"/>
       <c r="AW14" s="6" t="n"/>
     </row>
+    <row r="15">
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>2259801</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>한화생명 바로연금보험 무배당(종신연금형 일반형 개인형)</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>2259801</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>한화생명 바로연금보험 무배당(종신연금형 일반형 개인형)</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>X57</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>N0</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L15" t="n">
+        <v>57</v>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N15" t="n">
+        <v>0</v>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>2259801</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>한화생명 바로연금보험 무배당(종신연금형 일반형 개인형)</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>2259801</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>한화생명 바로연금보험 무배당(종신연금형 일반형 개인형)</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>X58</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>N0</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L16" t="n">
+        <v>58</v>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>2259801</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>한화생명 바로연금보험 무배당(종신연금형 일반형 개인형)</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>2259801</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>한화생명 바로연금보험 무배당(종신연금형 일반형 개인형)</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>X59</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>N0</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L17" t="n">
+        <v>59</v>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>2259801</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>한화생명 바로연금보험 무배당(종신연금형 일반형 개인형)</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>2259801</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>한화생명 바로연금보험 무배당(종신연금형 일반형 개인형)</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>X60</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>N0</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L18" t="n">
+        <v>60</v>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N18" t="n">
+        <v>0</v>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>2259801</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>한화생명 바로연금보험 무배당(종신연금형 일반형 개인형)</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>2259801</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>한화생명 바로연금보험 무배당(종신연금형 일반형 개인형)</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>X61</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>N0</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L19" t="n">
+        <v>61</v>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N19" t="n">
+        <v>0</v>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>2259801</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>한화생명 바로연금보험 무배당(종신연금형 일반형 개인형)</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>2259801</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>한화생명 바로연금보험 무배당(종신연금형 일반형 개인형)</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>X62</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>N0</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L20" t="n">
+        <v>62</v>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N20" t="n">
+        <v>0</v>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>2259801</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>한화생명 바로연금보험 무배당(종신연금형 일반형 개인형)</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>2259801</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>한화생명 바로연금보험 무배당(종신연금형 일반형 개인형)</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>X63</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>N0</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L21" t="n">
+        <v>63</v>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N21" t="n">
+        <v>0</v>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>2259801</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>한화생명 바로연금보험 무배당(종신연금형 일반형 개인형)</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>2259801</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>한화생명 바로연금보험 무배당(종신연금형 일반형 개인형)</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>X64</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>N0</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L22" t="n">
+        <v>64</v>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N22" t="n">
+        <v>0</v>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>2259801</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>한화생명 바로연금보험 무배당(종신연금형 일반형 개인형)</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>2259801</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>한화생명 바로연금보험 무배당(종신연금형 일반형 개인형)</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>X65</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>N0</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L23" t="n">
+        <v>65</v>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N23" t="n">
+        <v>0</v>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>2259801</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>한화생명 바로연금보험 무배당(종신연금형 일반형 개인형)</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>2259801</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>한화생명 바로연금보험 무배당(종신연금형 일반형 개인형)</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>X66</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>N0</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L24" t="n">
+        <v>66</v>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N24" t="n">
+        <v>0</v>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>2259801</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>한화생명 바로연금보험 무배당(종신연금형 일반형 개인형)</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>2259801</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>한화생명 바로연금보험 무배당(종신연금형 일반형 개인형)</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>X67</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>N0</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L25" t="n">
+        <v>67</v>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N25" t="n">
+        <v>0</v>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>2259801</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>한화생명 바로연금보험 무배당(종신연금형 일반형 개인형)</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>2259801</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>한화생명 바로연금보험 무배당(종신연금형 일반형 개인형)</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>X68</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>N0</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L26" t="n">
+        <v>68</v>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N26" t="n">
+        <v>0</v>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>2259801</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>한화생명 바로연금보험 무배당(종신연금형 일반형 개인형)</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>2259801</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>한화생명 바로연금보험 무배당(종신연금형 일반형 개인형)</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>X69</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>N0</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L27" t="n">
+        <v>69</v>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N27" t="n">
+        <v>0</v>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>2259801</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>한화생명 바로연금보험 무배당(종신연금형 일반형 개인형)</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>2259801</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>한화생명 바로연금보험 무배당(종신연금형 일반형 개인형)</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>X70</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>N0</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L28" t="n">
+        <v>70</v>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N28" t="n">
+        <v>0</v>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>2259801</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>한화생명 바로연금보험 무배당(종신연금형 일반형 개인형)</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>2259801</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>한화생명 바로연금보험 무배당(종신연금형 일반형 개인형)</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>X71</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>N0</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L29" t="n">
+        <v>71</v>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>2259801</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>한화생명 바로연금보험 무배당(종신연금형 일반형 개인형)</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>2259801</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>한화생명 바로연금보험 무배당(종신연금형 일반형 개인형)</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>X72</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>N0</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L30" t="n">
+        <v>72</v>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>2259801</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>한화생명 바로연금보험 무배당(종신연금형 일반형 개인형)</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>2259801</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>한화생명 바로연금보험 무배당(종신연금형 일반형 개인형)</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>X73</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>N0</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L31" t="n">
+        <v>73</v>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N31" t="n">
+        <v>0</v>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>2259801</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>한화생명 바로연금보험 무배당(종신연금형 일반형 개인형)</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>2259801</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>한화생명 바로연금보험 무배당(종신연금형 일반형 개인형)</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>X74</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>N0</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L32" t="n">
+        <v>74</v>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N32" t="n">
+        <v>0</v>
+      </c>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>2259801</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>한화생명 바로연금보험 무배당(종신연금형 일반형 개인형)</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>2259801</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>한화생명 바로연금보험 무배당(종신연금형 일반형 개인형)</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>X75</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>N0</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L33" t="n">
+        <v>75</v>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N33" t="n">
+        <v>0</v>
+      </c>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>2259801</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>한화생명 바로연금보험 무배당(종신연금형 일반형 개인형)</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>2259801</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>한화생명 바로연금보험 무배당(종신연금형 일반형 개인형)</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>X76</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>N0</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L34" t="n">
+        <v>76</v>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N34" t="n">
+        <v>0</v>
+      </c>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>2259801</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>한화생명 바로연금보험 무배당(종신연금형 일반형 개인형)</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>2259801</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>한화생명 바로연금보험 무배당(종신연금형 일반형 개인형)</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>X77</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>N0</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L35" t="n">
+        <v>77</v>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N35" t="n">
+        <v>0</v>
+      </c>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>2259801</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>한화생명 바로연금보험 무배당(종신연금형 일반형 개인형)</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>2259801</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>한화생명 바로연금보험 무배당(종신연금형 일반형 개인형)</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>X78</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>N0</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L36" t="n">
+        <v>78</v>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N36" t="n">
+        <v>0</v>
+      </c>
+      <c r="O36" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>2259801</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>한화생명 바로연금보험 무배당(종신연금형 일반형 개인형)</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>2259801</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>한화생명 바로연금보험 무배당(종신연금형 일반형 개인형)</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>X79</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>N0</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L37" t="n">
+        <v>79</v>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N37" t="n">
+        <v>0</v>
+      </c>
+      <c r="O37" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>2259801</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>한화생명 바로연금보험 무배당(종신연금형 일반형 개인형)</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>2259801</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>한화생명 바로연금보험 무배당(종신연금형 일반형 개인형)</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>X80</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>N0</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L38" t="n">
+        <v>80</v>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N38" t="n">
+        <v>0</v>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>2259801</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>한화생명 바로연금보험 무배당(종신연금형 일반형 개인형)</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>2259801</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>한화생명 바로연금보험 무배당(종신연금형 일반형 개인형)</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>X81</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>N0</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L39" t="n">
+        <v>81</v>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N39" t="n">
+        <v>0</v>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>2259801</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>한화생명 바로연금보험 무배당(종신연금형 일반형 개인형)</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>2259801</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>한화생명 바로연금보험 무배당(종신연금형 일반형 개인형)</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>X82</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>N0</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L40" t="n">
+        <v>82</v>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N40" t="n">
+        <v>0</v>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>2259801</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>한화생명 바로연금보험 무배당(종신연금형 일반형 개인형)</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>2259801</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>한화생명 바로연금보험 무배당(종신연금형 일반형 개인형)</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>X83</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>N0</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L41" t="n">
+        <v>83</v>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N41" t="n">
+        <v>0</v>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>2259801</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>한화생명 바로연금보험 무배당(종신연금형 일반형 개인형)</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>2259801</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>한화생명 바로연금보험 무배당(종신연금형 일반형 개인형)</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>X84</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>N0</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L42" t="n">
+        <v>84</v>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N42" t="n">
+        <v>0</v>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>2259801</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>한화생명 바로연금보험 무배당(종신연금형 일반형 개인형)</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>2259801</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>한화생명 바로연금보험 무배당(종신연금형 일반형 개인형)</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>X85</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>N0</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L43" t="n">
+        <v>85</v>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N43" t="n">
+        <v>0</v>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>2259801</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>한화생명 바로연금보험 무배당(종신연금형 일반형 개인형)</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>2259801</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>한화생명 바로연금보험 무배당(종신연금형 일반형 개인형)</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>X86</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>N0</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L44" t="n">
+        <v>86</v>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N44" t="n">
+        <v>0</v>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>2259801</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>한화생명 바로연금보험 무배당(종신연금형 일반형 개인형)</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>2259801</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>한화생명 바로연금보험 무배당(종신연금형 일반형 개인형)</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>X87</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>N0</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L45" t="n">
+        <v>87</v>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N45" t="n">
+        <v>0</v>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>2259801</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>한화생명 바로연금보험 무배당(종신연금형 일반형 개인형)</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>2259801</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>한화생명 바로연금보험 무배당(종신연금형 일반형 개인형)</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>X88</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>N0</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L46" t="n">
+        <v>88</v>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N46" t="n">
+        <v>0</v>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>2259801</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>한화생명 바로연금보험 무배당(종신연금형 일반형 개인형)</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>2259801</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>한화생명 바로연금보험 무배당(종신연금형 일반형 개인형)</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>X89</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>N0</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L47" t="n">
+        <v>89</v>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N47" t="n">
+        <v>0</v>
+      </c>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>2259801</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>한화생명 바로연금보험 무배당(종신연금형 일반형 개인형)</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>2259801</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>한화생명 바로연금보험 무배당(종신연금형 일반형 개인형)</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>X90</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>N0</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L48" t="n">
+        <v>90</v>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N48" t="n">
+        <v>0</v>
+      </c>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>2259801</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>한화생명 바로연금보험 무배당(종신연금형 일반형 개인형)</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>2259801</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>한화생명 바로연금보험 무배당(종신연금형 일반형 개인형)</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>X91</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>N0</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L49" t="n">
+        <v>91</v>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N49" t="n">
+        <v>0</v>
+      </c>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>2259801</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>한화생명 바로연금보험 무배당(종신연금형 일반형 개인형)</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>2259801</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>한화생명 바로연금보험 무배당(종신연금형 일반형 개인형)</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>X92</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>N0</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L50" t="n">
+        <v>92</v>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N50" t="n">
+        <v>0</v>
+      </c>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>2259801</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>한화생명 바로연금보험 무배당(종신연금형 일반형 개인형)</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>2259801</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>한화생명 바로연금보험 무배당(종신연금형 일반형 개인형)</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>X93</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>N0</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L51" t="n">
+        <v>93</v>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N51" t="n">
+        <v>0</v>
+      </c>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>2259801</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>한화생명 바로연금보험 무배당(종신연금형 일반형 개인형)</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>2259801</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>한화생명 바로연금보험 무배당(종신연금형 일반형 개인형)</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>X94</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>N0</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L52" t="n">
+        <v>94</v>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N52" t="n">
+        <v>0</v>
+      </c>
+      <c r="O52" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>2259801</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>한화생명 바로연금보험 무배당(종신연금형 일반형 개인형)</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>2259801</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>한화생명 바로연금보험 무배당(종신연금형 일반형 개인형)</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>X95</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>N0</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L53" t="n">
+        <v>95</v>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N53" t="n">
+        <v>0</v>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>2259801</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>한화생명 바로연금보험 무배당(종신연금형 일반형 개인형)</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>2259801</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>한화생명 바로연금보험 무배당(종신연금형 일반형 개인형)</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>X96</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>N0</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L54" t="n">
+        <v>96</v>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N54" t="n">
+        <v>0</v>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>2259801</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>한화생명 바로연금보험 무배당(종신연금형 일반형 개인형)</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>2259801</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>한화생명 바로연금보험 무배당(종신연금형 일반형 개인형)</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>X97</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>N0</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L55" t="n">
+        <v>97</v>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N55" t="n">
+        <v>0</v>
+      </c>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>2259801</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>한화생명 바로연금보험 무배당(종신연금형 일반형 개인형)</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>2259801</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>한화생명 바로연금보험 무배당(종신연금형 일반형 개인형)</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>X98</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>N0</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L56" t="n">
+        <v>98</v>
+      </c>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N56" t="n">
+        <v>0</v>
+      </c>
+      <c r="O56" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>2259801</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>한화생명 바로연금보험 무배당(종신연금형 일반형 개인형)</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>2259801</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>한화생명 바로연금보험 무배당(종신연금형 일반형 개인형)</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>X99</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>N0</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L57" t="n">
+        <v>99</v>
+      </c>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N57" t="n">
+        <v>0</v>
+      </c>
+      <c r="O57" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>2259801</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>한화생명 바로연금보험 무배당(종신연금형 일반형 개인형)</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>2259801</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>한화생명 바로연금보험 무배당(종신연금형 일반형 개인형)</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>X100</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>N0</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L58" t="n">
+        <v>100</v>
+      </c>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N58" t="n">
+        <v>0</v>
+      </c>
+      <c r="O58" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>2259801</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>한화생명 바로연금보험 무배당(종신연금형 일반형 개인형)</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>2259801</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>한화생명 바로연금보험 무배당(종신연금형 일반형 개인형)</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>X101</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>N0</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L59" t="n">
+        <v>101</v>
+      </c>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N59" t="n">
+        <v>0</v>
+      </c>
+      <c r="O59" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>2259801</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>한화생명 바로연금보험 무배당(종신연금형 일반형 개인형)</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>2259801</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>한화생명 바로연금보험 무배당(종신연금형 일반형 개인형)</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>X102</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>N0</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L60" t="n">
+        <v>102</v>
+      </c>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N60" t="n">
+        <v>0</v>
+      </c>
+      <c r="O60" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>2259801</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>한화생명 바로연금보험 무배당(종신연금형 일반형 개인형)</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>2259801</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>한화생명 바로연금보험 무배당(종신연금형 일반형 개인형)</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>X103</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>N0</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L61" t="n">
+        <v>103</v>
+      </c>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N61" t="n">
+        <v>0</v>
+      </c>
+      <c r="O61" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>2259801</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>한화생명 바로연금보험 무배당(종신연금형 일반형 개인형)</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>2259801</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>한화생명 바로연금보험 무배당(종신연금형 일반형 개인형)</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>X104</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>N0</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L62" t="n">
+        <v>104</v>
+      </c>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N62" t="n">
+        <v>0</v>
+      </c>
+      <c r="O62" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>2259801</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>한화생명 바로연금보험 무배당(종신연금형 일반형 개인형)</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>2259801</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>한화생명 바로연금보험 무배당(종신연금형 일반형 개인형)</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>X105</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>N0</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L63" t="n">
+        <v>105</v>
+      </c>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N63" t="n">
+        <v>0</v>
+      </c>
+      <c r="O63" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="6">
     <mergeCell ref="I3:N3"/>
